--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488279</v>
       </c>
       <c r="B2" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128488286</v>
       </c>
       <c r="B3" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128488915</v>
       </c>
       <c r="B4" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128535746</v>
       </c>
       <c r="B5" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128536507</v>
       </c>
       <c r="B6" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128536006</v>
       </c>
       <c r="B7" t="n">
-        <v>86774</v>
+        <v>86778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>128535841</v>
       </c>
       <c r="B8" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128535654</v>
+        <v>128535720</v>
       </c>
       <c r="B9" t="n">
-        <v>92776</v>
+        <v>92393</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128535720</v>
+        <v>128535654</v>
       </c>
       <c r="B10" t="n">
-        <v>92387</v>
+        <v>92782</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1466,21 +1466,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488279</v>
       </c>
       <c r="B2" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128488286</v>
       </c>
       <c r="B3" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128488915</v>
       </c>
       <c r="B4" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128535746</v>
       </c>
       <c r="B5" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128536507</v>
       </c>
       <c r="B6" t="n">
-        <v>86948</v>
+        <v>86954</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128536006</v>
       </c>
       <c r="B7" t="n">
-        <v>86778</v>
+        <v>86784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>128535841</v>
       </c>
       <c r="B8" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128535720</v>
+        <v>128535654</v>
       </c>
       <c r="B9" t="n">
-        <v>92393</v>
+        <v>92788</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128535654</v>
+        <v>128535720</v>
       </c>
       <c r="B10" t="n">
-        <v>92782</v>
+        <v>92399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1466,21 +1466,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128535654</v>
+        <v>128535720</v>
       </c>
       <c r="B9" t="n">
-        <v>92788</v>
+        <v>92399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128535720</v>
+        <v>128535654</v>
       </c>
       <c r="B10" t="n">
-        <v>92399</v>
+        <v>92788</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1466,21 +1466,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488279</v>
       </c>
       <c r="B2" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128488286</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128488915</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128535746</v>
       </c>
       <c r="B5" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128536507</v>
       </c>
       <c r="B6" t="n">
-        <v>86954</v>
+        <v>86956</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128536006</v>
       </c>
       <c r="B7" t="n">
-        <v>86784</v>
+        <v>86786</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>128535841</v>
       </c>
       <c r="B8" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>128535720</v>
       </c>
       <c r="B9" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128535654</v>
       </c>
       <c r="B10" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488279</v>
       </c>
       <c r="B2" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128488286</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128488915</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128535746</v>
       </c>
       <c r="B5" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>128535841</v>
       </c>
       <c r="B8" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>128535720</v>
       </c>
       <c r="B9" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128535654</v>
       </c>
       <c r="B10" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488279</v>
       </c>
       <c r="B2" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128488286</v>
       </c>
       <c r="B3" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128488915</v>
       </c>
       <c r="B4" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128535746</v>
       </c>
       <c r="B5" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128536507</v>
       </c>
       <c r="B6" t="n">
-        <v>86956</v>
+        <v>86983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128536006</v>
       </c>
       <c r="B7" t="n">
-        <v>86786</v>
+        <v>86813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>128535841</v>
       </c>
       <c r="B8" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128535720</v>
+        <v>128535654</v>
       </c>
       <c r="B9" t="n">
-        <v>92402</v>
+        <v>92818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128535654</v>
+        <v>128535720</v>
       </c>
       <c r="B10" t="n">
-        <v>92791</v>
+        <v>92429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1466,21 +1466,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1550,6 +1550,403 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128844215</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92818</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skogsbo, Skogsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>559511</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6680981</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128843600</v>
+      </c>
+      <c r="B12" t="n">
+        <v>86954</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skogsbo, Skogsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>559493</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6680592</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128843425</v>
+      </c>
+      <c r="B13" t="n">
+        <v>86756</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skogsbo, Skogsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>559493</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6680592</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128844556</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92773</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>150</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grangråticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Boletopsis leucomelaena</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Skogsbo, Skogsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>559505</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6680985</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128488279</v>
       </c>
       <c r="B2" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128488286</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128488915</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128535746</v>
       </c>
       <c r="B5" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128536507</v>
       </c>
       <c r="B6" t="n">
-        <v>86983</v>
+        <v>86987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128536006</v>
       </c>
       <c r="B7" t="n">
-        <v>86813</v>
+        <v>86817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>128535841</v>
       </c>
       <c r="B8" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,10 +1358,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128535654</v>
+        <v>128535720</v>
       </c>
       <c r="B9" t="n">
-        <v>92818</v>
+        <v>92434</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128535720</v>
+        <v>128535654</v>
       </c>
       <c r="B10" t="n">
-        <v>92429</v>
+        <v>92823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1466,21 +1466,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
         <v>128844215</v>
       </c>
       <c r="B11" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128843600</v>
       </c>
       <c r="B12" t="n">
-        <v>86954</v>
+        <v>86958</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128843425</v>
       </c>
       <c r="B13" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>128844556</v>
       </c>
       <c r="B14" t="n">
-        <v>92773</v>
+        <v>92778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128535746</v>
       </c>
       <c r="B5" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128536507</v>
       </c>
       <c r="B6" t="n">
-        <v>86999</v>
+        <v>87004</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128536006</v>
       </c>
       <c r="B7" t="n">
-        <v>86828</v>
+        <v>86833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>128535841</v>
       </c>
       <c r="B8" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>128535720</v>
       </c>
       <c r="B9" t="n">
-        <v>92451</v>
+        <v>92456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128535654</v>
       </c>
       <c r="B10" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1358,10 +1358,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128535720</v>
+        <v>128535654</v>
       </c>
       <c r="B9" t="n">
-        <v>92456</v>
+        <v>92847</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1369,21 +1369,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128535654</v>
+        <v>128535720</v>
       </c>
       <c r="B10" t="n">
-        <v>92847</v>
+        <v>92456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1466,21 +1466,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
         <v>128844215</v>
       </c>
       <c r="B11" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128843425</v>
       </c>
       <c r="B12" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128844556</v>
       </c>
       <c r="B13" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128843600</v>
       </c>
       <c r="B14" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>128535746</v>
       </c>
       <c r="B5" t="n">
-        <v>92847</v>
+        <v>92855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128536507</v>
       </c>
       <c r="B6" t="n">
-        <v>87004</v>
+        <v>87010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>128536006</v>
       </c>
       <c r="B7" t="n">
-        <v>86833</v>
+        <v>86839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>128535841</v>
       </c>
       <c r="B8" t="n">
-        <v>92847</v>
+        <v>92855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>128535654</v>
       </c>
       <c r="B9" t="n">
-        <v>92847</v>
+        <v>92855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128535720</v>
       </c>
       <c r="B10" t="n">
-        <v>92456</v>
+        <v>92464</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>128844215</v>
       </c>
       <c r="B11" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128843425</v>
       </c>
       <c r="B12" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128844556</v>
       </c>
       <c r="B13" t="n">
-        <v>92805</v>
+        <v>92808</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128843600</v>
       </c>
       <c r="B14" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>128844215</v>
       </c>
       <c r="B11" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128843425</v>
       </c>
       <c r="B12" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128844556</v>
       </c>
       <c r="B13" t="n">
-        <v>92808</v>
+        <v>92815</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128843600</v>
       </c>
       <c r="B14" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>128844215</v>
       </c>
       <c r="B11" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128843425</v>
       </c>
       <c r="B12" t="n">
-        <v>86786</v>
+        <v>86793</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128844556</v>
       </c>
       <c r="B13" t="n">
-        <v>92815</v>
+        <v>92822</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128843600</v>
       </c>
       <c r="B14" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>128844215</v>
       </c>
       <c r="B11" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128843425</v>
       </c>
       <c r="B12" t="n">
-        <v>86793</v>
+        <v>86795</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128844556</v>
       </c>
       <c r="B13" t="n">
-        <v>92822</v>
+        <v>92824</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128843600</v>
       </c>
       <c r="B14" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>128844215</v>
       </c>
       <c r="B11" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128843425</v>
       </c>
       <c r="B12" t="n">
-        <v>86795</v>
+        <v>86796</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128844556</v>
       </c>
       <c r="B13" t="n">
-        <v>92824</v>
+        <v>92810</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128843600</v>
       </c>
       <c r="B14" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>128844215</v>
       </c>
       <c r="B11" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128844556</v>
       </c>
       <c r="B13" t="n">
-        <v>92810</v>
+        <v>92811</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1555,7 +1555,7 @@
         <v>128844215</v>
       </c>
       <c r="B11" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>128843425</v>
       </c>
       <c r="B12" t="n">
-        <v>86796</v>
+        <v>86799</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>128844556</v>
       </c>
       <c r="B13" t="n">
-        <v>92811</v>
+        <v>92814</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>128843600</v>
       </c>
       <c r="B14" t="n">
-        <v>86995</v>
+        <v>86998</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1855,7 +1855,7 @@
         <v>128843600</v>
       </c>
       <c r="B14" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1855,7 +1855,7 @@
         <v>128843600</v>
       </c>
       <c r="B14" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1855,7 +1855,7 @@
         <v>128843600</v>
       </c>
       <c r="B14" t="n">
-        <v>87004</v>
+        <v>87005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>128536006</v>
       </c>
       <c r="B7" t="n">
-        <v>86839</v>
+        <v>86912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1167,32 +1167,35 @@
         <v>128536006</v>
       </c>
       <c r="B7" t="n">
-        <v>86912</v>
+        <v>86907</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>248952</v>
+        <v>427</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåfotad fagerspindling</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius barbaricus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brandrud) Frøslev &amp; al.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Slössviken, Slössviken, Dlr</t>
@@ -1243,6 +1246,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>128536006</v>
       </c>
       <c r="B7" t="n">
-        <v>86907</v>
+        <v>86908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>128536006</v>
       </c>
       <c r="B7" t="n">
-        <v>86908</v>
+        <v>86925</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>128536006</v>
       </c>
       <c r="B7" t="n">
-        <v>86941</v>
+        <v>87028</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128488279</v>
+        <v>128844556</v>
       </c>
       <c r="B2" t="n">
-        <v>92842</v>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pers.) Fayod</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skogsbo, Skogsbo, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559447</v>
+        <v>559505</v>
       </c>
       <c r="R2" t="n">
-        <v>6680686</v>
+        <v>6680985</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -740,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,45 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128488286</v>
+        <v>128536006</v>
       </c>
       <c r="B3" t="n">
-        <v>92451</v>
+        <v>87196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>427</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogsbo, Skogsbo, Dlr</t>
+          <t>Slössviken, Slössviken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559432</v>
+        <v>559402</v>
       </c>
       <c r="R3" t="n">
-        <v>6680685</v>
+        <v>6680903</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -837,12 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -851,6 +863,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,45 +882,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128488915</v>
+        <v>128536507</v>
       </c>
       <c r="B4" t="n">
-        <v>92451</v>
+        <v>87375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>3739</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skogsbo, Skogsbo, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559478</v>
+        <v>559571</v>
       </c>
       <c r="R4" t="n">
-        <v>6680552</v>
+        <v>6681009</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -934,12 +950,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -948,6 +964,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -966,10 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128535746</v>
+        <v>128843425</v>
       </c>
       <c r="B5" t="n">
-        <v>92855</v>
+        <v>87146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +994,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slössviken, Slössviken, Dlr</t>
+          <t>Skogsbo, Skogsbo, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559363</v>
+        <v>559493</v>
       </c>
       <c r="R5" t="n">
-        <v>6680847</v>
+        <v>6680592</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1031,12 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,48 +1080,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128536507</v>
+        <v>128843610</v>
       </c>
       <c r="B6" t="n">
-        <v>87010</v>
+        <v>87146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3739</v>
+        <v>3762</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skogsbo, Skogsbo, Dlr</t>
+          <t>Slössviken, Slössviken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559571</v>
+        <v>559371</v>
       </c>
       <c r="R6" t="n">
-        <v>6681009</v>
+        <v>6680901</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1131,12 +1145,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1145,7 +1159,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1164,48 +1177,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128536006</v>
+        <v>128488286</v>
       </c>
       <c r="B7" t="n">
-        <v>87028</v>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>427</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Slössviken, Slössviken, Dlr</t>
+          <t>Skogsbo, Skogsbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>559402</v>
+        <v>559432</v>
       </c>
       <c r="R7" t="n">
-        <v>6680903</v>
+        <v>6680685</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1232,12 +1242,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1246,7 +1256,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1265,10 +1274,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128535841</v>
+        <v>128488915</v>
       </c>
       <c r="B8" t="n">
-        <v>92855</v>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,34 +1285,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slössviken, Slössviken, Dlr</t>
+          <t>Skogsbo, Skogsbo, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>559402</v>
+        <v>559478</v>
       </c>
       <c r="R8" t="n">
-        <v>6680903</v>
+        <v>6680552</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1330,12 +1339,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,10 +1371,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128535654</v>
+        <v>128535720</v>
       </c>
       <c r="B9" t="n">
-        <v>92855</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1373,21 +1382,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128535720</v>
+        <v>128843761</v>
       </c>
       <c r="B10" t="n">
-        <v>92464</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1490,14 +1499,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rensboberget, Rensboberget, Dlr</t>
+          <t>Slössviken, Slössviken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>559311</v>
+        <v>559386</v>
       </c>
       <c r="R10" t="n">
-        <v>6680527</v>
+        <v>6680917</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1524,12 +1533,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1556,14 +1565,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128844215</v>
+        <v>128488279</v>
       </c>
       <c r="B11" t="n">
-        <v>92861</v>
+        <v>93233</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1591,10 +1600,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>559511</v>
+        <v>559447</v>
       </c>
       <c r="R11" t="n">
-        <v>6680981</v>
+        <v>6680686</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1621,12 +1630,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1653,45 +1662,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128843425</v>
+        <v>128488355</v>
       </c>
       <c r="B12" t="n">
-        <v>86799</v>
+        <v>93233</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3762</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skogsbo, Skogsbo, Dlr</t>
+          <t>Rensboberget, Rensboberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>559493</v>
+        <v>559330</v>
       </c>
       <c r="R12" t="n">
-        <v>6680592</v>
+        <v>6680795</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1718,12 +1730,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1732,6 +1744,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1750,54 +1763,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128844556</v>
+        <v>128535654</v>
       </c>
       <c r="B13" t="n">
-        <v>92814</v>
+        <v>93233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>150</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skogsbo, Skogsbo, Dlr</t>
+          <t>Rensboberget, Rensboberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>559505</v>
+        <v>559311</v>
       </c>
       <c r="R13" t="n">
-        <v>6680985</v>
+        <v>6680527</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1824,12 +1828,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1856,10 +1860,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128843600</v>
+        <v>128535746</v>
       </c>
       <c r="B14" t="n">
-        <v>87005</v>
+        <v>93233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1867,37 +1871,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6003295</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Slössviken, Slössviken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>559402</v>
+        <v>559363</v>
       </c>
       <c r="R14" t="n">
-        <v>6680903</v>
+        <v>6680847</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1924,12 +1925,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1938,7 +1939,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1954,6 +1954,689 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128535841</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Slössviken, Slössviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>559402</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6680903</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128536237</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Uvberget, Uvberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>559499</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6680995</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128536249</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Uvberget, Uvberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>559493</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6681006</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128843633</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Slössviken, Slössviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>559386</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6680917</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128844215</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skogsbo, Skogsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>559511</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6680981</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128844703</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Uvberget, Uvberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>559512</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6681004</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128843600</v>
+      </c>
+      <c r="B21" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Slössviken, Slössviken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>559402</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6680903</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38725-2025 artfynd.xlsx
+++ b/artfynd/A 38725-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128844556</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128536006</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128536507</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128843425</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128843610</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128488286</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1368,6 +1403,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128488915</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1465,6 +1505,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128535720</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1562,6 +1607,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128843761</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1659,6 +1709,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128488279</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1760,6 +1815,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128488355</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1857,6 +1917,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128535654</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1954,6 +2019,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128535746</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2051,6 +2121,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128535841</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2148,6 +2223,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128536237</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2245,6 +2325,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128536249</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2342,6 +2427,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128843633</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2439,6 +2529,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128844215</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2536,6 +2631,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128844703</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2637,8 +2737,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128843600</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>